--- a/Snailcraft Items.xlsx
+++ b/Snailcraft Items.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/aaad0b26e5206fe0/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10308" documentId="8_{46A8860C-ED55-43FC-8D9E-18FE673E99B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D7171C53-247E-4EB1-A40E-B53F37698997}"/>
+  <xr:revisionPtr revIDLastSave="10318" documentId="8_{46A8860C-ED55-43FC-8D9E-18FE673E99B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{656A18FC-21B6-45EB-BD49-F07634A8B8C7}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{50002386-2FD5-468D-85D2-09B9177736E2}"/>
   </bookViews>
@@ -29,7 +29,6 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Wearables!$A$1:$H$189</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -57,7 +56,7 @@
   <metadataTypes count="1">
     <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="1568">
+  <futureMetadata name="XLRICHVALUE" count="1569">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -11034,8 +11033,15 @@
         </ext>
       </extLst>
     </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="1568"/>
+        </ext>
+      </extLst>
+    </bk>
   </futureMetadata>
-  <valueMetadata count="1568">
+  <valueMetadata count="1569">
     <bk>
       <rc t="1" v="0"/>
     </bk>
@@ -15739,13 +15745,16 @@
     </bk>
     <bk>
       <rc t="1" v="1567"/>
+    </bk>
+    <bk>
+      <rc t="1" v="1568"/>
     </bk>
   </valueMetadata>
 </metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11671" uniqueCount="3334">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11678" uniqueCount="3337">
   <si>
     <t>Name</t>
   </si>
@@ -25927,6 +25936,15 @@
   </si>
   <si>
     <t>Exchange 2 for 3 Creepy Crawly Coins</t>
+  </si>
+  <si>
+    <t>Creepy Crawly Coin</t>
+  </si>
+  <si>
+    <t>Exchange BFG Insects for Coins</t>
+  </si>
+  <si>
+    <t>Halloween 2026 Crate Key</t>
   </si>
 </sst>
 </file>
@@ -26207,7 +26225,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1568">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1569">
   <rv s="0">
     <v>0</v>
     <v>5</v>
@@ -32478,6 +32496,10 @@
   </rv>
   <rv s="0">
     <v>1567</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>1568</v>
     <v>5</v>
   </rv>
 </rvData>
@@ -34062,6 +34084,7 @@
   <rel r:id="rId1566"/>
   <rel r:id="rId1567"/>
   <rel r:id="rId1568"/>
+  <rel r:id="rId1569"/>
 </richValueRels>
 </file>
 
@@ -57329,7 +57352,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90510ACF-0CB9-4E0D-8F8E-837E9DAF74EA}">
-  <dimension ref="A1:L787"/>
+  <dimension ref="A1:L788"/>
   <sheetFormatPr defaultRowHeight="45" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="29.7109375" bestFit="1" customWidth="1"/>
@@ -70264,7 +70287,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="B505" s="17" t="s">
-        <v>2495</v>
+        <v>3336</v>
       </c>
       <c r="C505" s="23" t="s">
         <v>2522</v>
@@ -77309,6 +77332,32 @@
         <v>2725</v>
       </c>
       <c r="H787" s="1" t="s">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="788" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A788" t="e" vm="1538">
+        <v>#VALUE!</v>
+      </c>
+      <c r="B788" t="s">
+        <v>3334</v>
+      </c>
+      <c r="C788" t="s">
+        <v>3335</v>
+      </c>
+      <c r="D788" s="3" t="s">
+        <v>1470</v>
+      </c>
+      <c r="E788" s="3" t="s">
+        <v>3087</v>
+      </c>
+      <c r="F788" s="1" t="s">
+        <v>968</v>
+      </c>
+      <c r="G788" s="1" t="s">
+        <v>1693</v>
+      </c>
+      <c r="H788" s="1" t="s">
         <v>1500</v>
       </c>
     </row>
@@ -77350,7 +77399,7 @@
       </c>
     </row>
     <row r="2" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="e" vm="1538">
+      <c r="A2" s="7" t="e" vm="1539">
         <v>#VALUE!</v>
       </c>
       <c r="B2" s="10" t="s">
@@ -77370,7 +77419,7 @@
       </c>
     </row>
     <row r="3" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="e" vm="1538">
+      <c r="A3" s="7" t="e" vm="1539">
         <v>#VALUE!</v>
       </c>
       <c r="B3" s="11" t="s">
@@ -77391,7 +77440,7 @@
       <c r="H3" s="4"/>
     </row>
     <row r="4" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" t="e" vm="1539">
+      <c r="A4" t="e" vm="1540">
         <v>#VALUE!</v>
       </c>
       <c r="B4" s="11" t="s">
@@ -77411,7 +77460,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="e" vm="1540">
+      <c r="A5" s="7" t="e" vm="1541">
         <v>#VALUE!</v>
       </c>
       <c r="B5" s="11" t="s">
@@ -77431,7 +77480,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="e" vm="1541">
+      <c r="A6" s="7" t="e" vm="1542">
         <v>#VALUE!</v>
       </c>
       <c r="B6" s="11" t="s">
@@ -77451,7 +77500,7 @@
       </c>
     </row>
     <row r="7" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="e" vm="1541">
+      <c r="A7" s="7" t="e" vm="1542">
         <v>#VALUE!</v>
       </c>
       <c r="B7" s="11" t="s">
@@ -77471,7 +77520,7 @@
       </c>
     </row>
     <row r="8" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="e" vm="1541">
+      <c r="A8" s="7" t="e" vm="1542">
         <v>#VALUE!</v>
       </c>
       <c r="B8" s="11" t="s">
@@ -77491,7 +77540,7 @@
       </c>
     </row>
     <row r="9" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="e" vm="1542">
+      <c r="A9" s="7" t="e" vm="1543">
         <v>#VALUE!</v>
       </c>
       <c r="B9" s="11" t="s">
@@ -77511,7 +77560,7 @@
       </c>
     </row>
     <row r="10" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="e" vm="1542">
+      <c r="A10" s="7" t="e" vm="1543">
         <v>#VALUE!</v>
       </c>
       <c r="B10" s="11" t="s">
@@ -77531,7 +77580,7 @@
       </c>
     </row>
     <row r="11" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="7" t="e" vm="1542">
+      <c r="A11" s="7" t="e" vm="1543">
         <v>#VALUE!</v>
       </c>
       <c r="B11" s="11" t="s">
@@ -77551,7 +77600,7 @@
       </c>
     </row>
     <row r="12" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="e" vm="1543">
+      <c r="A12" s="7" t="e" vm="1544">
         <v>#VALUE!</v>
       </c>
       <c r="B12" s="11" t="s">
@@ -77571,7 +77620,7 @@
       </c>
     </row>
     <row r="13" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="e" vm="1544">
+      <c r="A13" s="7" t="e" vm="1545">
         <v>#VALUE!</v>
       </c>
       <c r="B13" s="11" t="s">
@@ -77591,7 +77640,7 @@
       </c>
     </row>
     <row r="14" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="7" t="e" vm="1545">
+      <c r="A14" s="7" t="e" vm="1546">
         <v>#VALUE!</v>
       </c>
       <c r="B14" s="11" t="s">
@@ -77611,7 +77660,7 @@
       </c>
     </row>
     <row r="15" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="7" t="e" vm="1546">
+      <c r="A15" s="7" t="e" vm="1547">
         <v>#VALUE!</v>
       </c>
       <c r="B15" s="11" t="s">
@@ -77629,7 +77678,7 @@
       </c>
     </row>
     <row r="16" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="7" t="e" vm="1547">
+      <c r="A16" s="7" t="e" vm="1548">
         <v>#VALUE!</v>
       </c>
       <c r="B16" s="11" t="s">
@@ -77649,7 +77698,7 @@
       </c>
     </row>
     <row r="17" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="7" t="e" vm="1548">
+      <c r="A17" s="7" t="e" vm="1549">
         <v>#VALUE!</v>
       </c>
       <c r="B17" s="11" t="s">
@@ -77667,7 +77716,7 @@
       </c>
     </row>
     <row r="18" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="7" t="e" vm="1549">
+      <c r="A18" s="7" t="e" vm="1550">
         <v>#VALUE!</v>
       </c>
       <c r="B18" s="11" t="s">
@@ -77683,7 +77732,7 @@
       </c>
     </row>
     <row r="19" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="7" t="e" vm="1550">
+      <c r="A19" s="7" t="e" vm="1551">
         <v>#VALUE!</v>
       </c>
       <c r="B19" s="11" t="s">
@@ -77703,7 +77752,7 @@
       </c>
     </row>
     <row r="20" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="7" t="e" vm="1551">
+      <c r="A20" s="7" t="e" vm="1552">
         <v>#VALUE!</v>
       </c>
       <c r="B20" s="11" t="s">
@@ -77723,7 +77772,7 @@
       </c>
     </row>
     <row r="21" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="7" t="e" vm="1552">
+      <c r="A21" s="7" t="e" vm="1553">
         <v>#VALUE!</v>
       </c>
       <c r="B21" s="11" t="s">
@@ -77743,7 +77792,7 @@
       </c>
     </row>
     <row r="22" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="7" t="e" vm="1553">
+      <c r="A22" s="7" t="e" vm="1554">
         <v>#VALUE!</v>
       </c>
       <c r="B22" s="11" t="s">
@@ -77759,7 +77808,7 @@
       </c>
     </row>
     <row r="23" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="10" t="e" vm="1554">
+      <c r="A23" s="10" t="e" vm="1555">
         <v>#VALUE!</v>
       </c>
       <c r="B23" s="10" t="s">
@@ -77777,7 +77826,7 @@
       </c>
     </row>
     <row r="24" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="10" t="e" vm="1555">
+      <c r="A24" s="10" t="e" vm="1556">
         <v>#VALUE!</v>
       </c>
       <c r="B24" s="10" t="s">
@@ -77795,7 +77844,7 @@
       </c>
     </row>
     <row r="25" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="7" t="e" vm="1552">
+      <c r="A25" s="7" t="e" vm="1553">
         <v>#VALUE!</v>
       </c>
       <c r="B25" s="20" t="s">
@@ -77815,7 +77864,7 @@
       </c>
     </row>
     <row r="26" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" t="e" vm="1556">
+      <c r="A26" t="e" vm="1557">
         <v>#VALUE!</v>
       </c>
       <c r="B26" s="20" t="s">
@@ -77832,7 +77881,7 @@
       </c>
     </row>
     <row r="27" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="7" t="e" vm="1550">
+      <c r="A27" s="7" t="e" vm="1551">
         <v>#VALUE!</v>
       </c>
       <c r="B27" s="20" t="s">
@@ -77849,7 +77898,7 @@
       </c>
     </row>
     <row r="28" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" t="e" vm="1548">
+      <c r="A28" t="e" vm="1549">
         <v>#VALUE!</v>
       </c>
       <c r="B28" s="20" t="s">
@@ -77863,7 +77912,7 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" t="e" vm="1557">
+      <c r="A29" t="e" vm="1558">
         <v>#VALUE!</v>
       </c>
       <c r="B29" s="20" t="s">
@@ -77875,7 +77924,7 @@
       </c>
     </row>
     <row r="30" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" t="e" vm="1557">
+      <c r="A30" t="e" vm="1558">
         <v>#VALUE!</v>
       </c>
       <c r="B30" s="20" t="s">
@@ -77892,7 +77941,7 @@
       </c>
     </row>
     <row r="31" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" t="e" vm="1558">
+      <c r="A31" t="e" vm="1559">
         <v>#VALUE!</v>
       </c>
       <c r="B31" s="20" t="s">
@@ -77909,7 +77958,7 @@
       </c>
     </row>
     <row r="32" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" t="e" vm="1558">
+      <c r="A32" t="e" vm="1559">
         <v>#VALUE!</v>
       </c>
       <c r="B32" s="20" t="s">
@@ -77926,7 +77975,7 @@
       </c>
     </row>
     <row r="33" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" t="e" vm="1558">
+      <c r="A33" t="e" vm="1559">
         <v>#VALUE!</v>
       </c>
       <c r="B33" s="20" t="s">
@@ -77943,7 +77992,7 @@
       </c>
     </row>
     <row r="34" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" t="e" vm="1539">
+      <c r="A34" t="e" vm="1540">
         <v>#VALUE!</v>
       </c>
       <c r="B34" s="20" t="s">
@@ -77960,7 +78009,7 @@
       </c>
     </row>
     <row r="35" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" t="e" vm="1539">
+      <c r="A35" t="e" vm="1540">
         <v>#VALUE!</v>
       </c>
       <c r="B35" s="20" t="s">
@@ -77977,7 +78026,7 @@
       </c>
     </row>
     <row r="36" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" t="e" vm="1559">
+      <c r="A36" t="e" vm="1560">
         <v>#VALUE!</v>
       </c>
       <c r="B36" s="20" t="s">
@@ -77994,7 +78043,7 @@
       </c>
     </row>
     <row r="37" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" t="e" vm="1559">
+      <c r="A37" t="e" vm="1560">
         <v>#VALUE!</v>
       </c>
       <c r="B37" s="20" t="s">
@@ -78011,7 +78060,7 @@
       </c>
     </row>
     <row r="38" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" t="e" vm="1560">
+      <c r="A38" t="e" vm="1561">
         <v>#VALUE!</v>
       </c>
       <c r="B38" s="20" t="s">
@@ -78028,7 +78077,7 @@
       </c>
     </row>
     <row r="39" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" t="e" vm="1560">
+      <c r="A39" t="e" vm="1561">
         <v>#VALUE!</v>
       </c>
       <c r="B39" s="20" t="s">
@@ -78045,7 +78094,7 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" t="e" vm="1561">
+      <c r="A40" t="e" vm="1562">
         <v>#VALUE!</v>
       </c>
       <c r="B40" s="20" t="s">
@@ -78062,7 +78111,7 @@
       </c>
     </row>
     <row r="41" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" t="e" vm="1562">
+      <c r="A41" t="e" vm="1563">
         <v>#VALUE!</v>
       </c>
       <c r="B41" s="20" t="s">
@@ -78079,7 +78128,7 @@
       </c>
     </row>
     <row r="42" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" t="e" vm="1562">
+      <c r="A42" t="e" vm="1563">
         <v>#VALUE!</v>
       </c>
       <c r="B42" s="20" t="s">
@@ -78096,7 +78145,7 @@
       </c>
     </row>
     <row r="43" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" t="e" vm="1563">
+      <c r="A43" t="e" vm="1564">
         <v>#VALUE!</v>
       </c>
       <c r="B43" s="20" t="s">
@@ -78113,7 +78162,7 @@
       </c>
     </row>
     <row r="44" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" t="e" vm="1563">
+      <c r="A44" t="e" vm="1564">
         <v>#VALUE!</v>
       </c>
       <c r="B44" s="20" t="s">
@@ -78130,7 +78179,7 @@
       </c>
     </row>
     <row r="45" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" t="e" vm="1564">
+      <c r="A45" t="e" vm="1565">
         <v>#VALUE!</v>
       </c>
       <c r="B45" s="20" t="s">
@@ -78147,7 +78196,7 @@
       </c>
     </row>
     <row r="46" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" t="e" vm="1565">
+      <c r="A46" t="e" vm="1566">
         <v>#VALUE!</v>
       </c>
       <c r="B46" s="20" t="s">
@@ -78159,7 +78208,7 @@
       </c>
     </row>
     <row r="47" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" t="e" vm="1565">
+      <c r="A47" t="e" vm="1566">
         <v>#VALUE!</v>
       </c>
       <c r="B47" s="20" t="s">
@@ -78176,7 +78225,7 @@
       </c>
     </row>
     <row r="48" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" t="e" vm="1565">
+      <c r="A48" t="e" vm="1566">
         <v>#VALUE!</v>
       </c>
       <c r="B48" s="20" t="s">
@@ -78191,7 +78240,7 @@
       </c>
     </row>
     <row r="49" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" t="e" vm="1559">
+      <c r="A49" t="e" vm="1560">
         <v>#VALUE!</v>
       </c>
       <c r="B49" s="20" t="s">
@@ -78206,7 +78255,7 @@
       </c>
     </row>
     <row r="50" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" t="e" vm="1565">
+      <c r="A50" t="e" vm="1566">
         <v>#VALUE!</v>
       </c>
       <c r="B50" s="20" t="s">
@@ -78223,7 +78272,7 @@
       </c>
     </row>
     <row r="51" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" t="e" vm="1561">
+      <c r="A51" t="e" vm="1562">
         <v>#VALUE!</v>
       </c>
       <c r="B51" s="20" t="s">
@@ -78238,7 +78287,7 @@
       </c>
     </row>
     <row r="52" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="7" t="e" vm="1552">
+      <c r="A52" s="7" t="e" vm="1553">
         <v>#VALUE!</v>
       </c>
       <c r="B52" s="11" t="s">
@@ -78259,7 +78308,7 @@
       <c r="G52" s="23"/>
     </row>
     <row r="53" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="7" t="e" vm="1538">
+      <c r="A53" s="7" t="e" vm="1539">
         <v>#VALUE!</v>
       </c>
       <c r="B53" s="20" t="s">
@@ -78276,7 +78325,7 @@
       </c>
     </row>
     <row r="54" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="7" t="e" vm="1566">
+      <c r="A54" s="7" t="e" vm="1567">
         <v>#VALUE!</v>
       </c>
       <c r="B54" s="20" t="s">
@@ -78293,7 +78342,7 @@
       </c>
     </row>
     <row r="55" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" t="e" vm="1567">
+      <c r="A55" t="e" vm="1568">
         <v>#VALUE!</v>
       </c>
       <c r="B55" s="20" t="s">
@@ -78310,7 +78359,7 @@
       </c>
     </row>
     <row r="56" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" t="e" vm="1568">
+      <c r="A56" t="e" vm="1569">
         <v>#VALUE!</v>
       </c>
       <c r="B56" s="20" t="s">
@@ -78327,7 +78376,7 @@
       </c>
     </row>
     <row r="57" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="7" t="e" vm="1566">
+      <c r="A57" s="7" t="e" vm="1567">
         <v>#VALUE!</v>
       </c>
       <c r="B57" s="20" t="s">
